--- a/SETxHES/RtePM-Jan2026/scenarios_table_layout.xlsx
+++ b/SETxHES/RtePM-Jan2026/scenarios_table_layout.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abuabara/Downloads/Transportation/GIS-RtePM-Jan2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abuabara/Documents/GitHub/abuabara.github.io/SETxHES/RtePM-Jan2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B98158-318E-574D-8B7A-781B78662636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCA4769-A8C7-9348-824D-82A681D79B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="16860" xr2:uid="{781838FF-B15F-9244-9534-2D1ADBD596E4}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
   <si>
     <t>Up-Mid_B-15</t>
   </si>
@@ -204,6 +204,12 @@
   </si>
   <si>
     <t>Lower_B-31</t>
+  </si>
+  <si>
+    <t>Up-Mid_B-45E</t>
+  </si>
+  <si>
+    <t>Up-Mid_B-46E</t>
   </si>
 </sst>
 </file>
@@ -672,7 +678,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -689,12 +695,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -794,6 +794,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -807,15 +816,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1158,482 +1158,486 @@
   <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" style="34" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" style="39" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" style="37" customWidth="1"/>
     <col min="3" max="12" width="11.6640625" style="1" customWidth="1"/>
     <col min="13" max="14" width="14.6640625" style="1" customWidth="1"/>
     <col min="15" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="28"/>
-      <c r="B1" s="44" t="s">
+      <c r="A1" s="26"/>
+      <c r="B1" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="41" t="s">
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="41" t="s">
+      <c r="F1" s="43"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="42"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="41" t="s">
+      <c r="I1" s="43"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="44"/>
     </row>
     <row r="2" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="F2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="48" t="s">
+      <c r="G2" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="46" t="s">
+      <c r="H2" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="I2" s="47" t="s">
+      <c r="I2" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="J2" s="48" t="s">
+      <c r="J2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="46" t="s">
+      <c r="K2" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="L2" s="47" t="s">
+      <c r="L2" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="M2" s="11"/>
-      <c r="N2" s="12"/>
+      <c r="M2" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="3" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="8"/>
-      <c r="N3" s="9"/>
+      <c r="B3" s="33"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="22"/>
     </row>
     <row r="4" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="36"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="3"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="12"/>
     </row>
     <row r="5" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="31" t="s">
+      <c r="A5" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="3"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="17"/>
+      <c r="N5" s="12"/>
     </row>
     <row r="6" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="31" t="s">
+      <c r="A6" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="3"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="16"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="17"/>
+      <c r="N6" s="12"/>
     </row>
     <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="3"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="16"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="12"/>
     </row>
     <row r="8" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="3"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="16"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="17"/>
+      <c r="N8" s="12"/>
     </row>
     <row r="9" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="3"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="17"/>
+      <c r="N9" s="12"/>
     </row>
     <row r="10" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="37"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="21"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="7"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="13"/>
     </row>
     <row r="11" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="36" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I11" s="11" t="s">
+      <c r="I11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="M11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="N11" s="12" t="s">
+      <c r="N11" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="35"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="24"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="22"/>
     </row>
     <row r="13" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="36"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="14"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="17"/>
+      <c r="M13" s="17"/>
+      <c r="N13" s="12"/>
     </row>
     <row r="14" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="31" t="s">
+      <c r="A14" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="36"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="19"/>
-      <c r="M14" s="19"/>
-      <c r="N14" s="14"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="17"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="16"/>
+      <c r="L14" s="17"/>
+      <c r="M14" s="17"/>
+      <c r="N14" s="12"/>
     </row>
     <row r="15" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="19"/>
-      <c r="M15" s="19"/>
-      <c r="N15" s="14"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="16"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="16"/>
+      <c r="L15" s="17"/>
+      <c r="M15" s="17"/>
+      <c r="N15" s="12"/>
     </row>
     <row r="16" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="32" t="s">
+      <c r="A16" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="37"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="21"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="21"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="21"/>
-      <c r="M16" s="21"/>
-      <c r="N16" s="15"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="19"/>
+      <c r="M16" s="19"/>
+      <c r="N16" s="13"/>
     </row>
     <row r="17" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="38" t="s">
+      <c r="B17" s="36" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="I17" s="11" t="s">
+      <c r="I17" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="J17" s="12" t="s">
+      <c r="J17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="L17" s="11" t="s">
+      <c r="L17" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="M17" s="11"/>
-      <c r="N17" s="12"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="10"/>
     </row>
     <row r="18" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="9"/>
+      <c r="B18" s="33"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="7"/>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="19"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="17"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="17"/>
       <c r="M19" s="2"/>
       <c r="N19" s="3"/>
     </row>
     <row r="20" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="31" t="s">
+      <c r="A20" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="19"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="17"/>
       <c r="M20" s="2"/>
       <c r="N20" s="3"/>
     </row>
     <row r="21" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="36"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="19"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="17"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="17"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="17"/>
       <c r="M21" s="2"/>
       <c r="N21" s="3"/>
     </row>
     <row r="22" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="33" t="s">
+      <c r="A22" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="40"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="26"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="22"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="20"/>
       <c r="M22" s="4"/>
       <c r="N22" s="5"/>
     </row>

--- a/SETxHES/RtePM-Jan2026/scenarios_table_layout.xlsx
+++ b/SETxHES/RtePM-Jan2026/scenarios_table_layout.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abuabara/Documents/GitHub/abuabara.github.io/SETxHES/RtePM-Jan2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DCA4769-A8C7-9348-824D-82A681D79B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFC2FFA-749D-9A46-83EA-D4B1F2D7F242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="16860" xr2:uid="{781838FF-B15F-9244-9534-2D1ADBD596E4}"/>
   </bookViews>
@@ -1160,8 +1160,8 @@
   <cols>
     <col min="1" max="1" width="14.33203125" style="32" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.83203125" style="37" customWidth="1"/>
-    <col min="3" max="12" width="11.6640625" style="1" customWidth="1"/>
-    <col min="13" max="14" width="14.6640625" style="1" customWidth="1"/>
+    <col min="3" max="10" width="11.6640625" style="1" customWidth="1"/>
+    <col min="11" max="14" width="13.83203125" style="1" customWidth="1"/>
     <col min="15" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>

--- a/SETxHES/RtePM-Jan2026/scenarios_table_layout.xlsx
+++ b/SETxHES/RtePM-Jan2026/scenarios_table_layout.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abuabara/Documents/GitHub/abuabara.github.io/SETxHES/RtePM-Jan2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEFC2FFA-749D-9A46-83EA-D4B1F2D7F242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF0DE0C8-2216-F144-9D63-D206DE768910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="700" windowWidth="27040" windowHeight="16860" xr2:uid="{781838FF-B15F-9244-9534-2D1ADBD596E4}"/>
+    <workbookView xWindow="-20" yWindow="700" windowWidth="27040" windowHeight="16860" xr2:uid="{781838FF-B15F-9244-9534-2D1ADBD596E4}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
   <si>
     <t>Up-Mid_B-15</t>
   </si>
@@ -204,12 +204,6 @@
   </si>
   <si>
     <t>Lower_B-31</t>
-  </si>
-  <si>
-    <t>Up-Mid_B-45E</t>
-  </si>
-  <si>
-    <t>Up-Mid_B-46E</t>
   </si>
 </sst>
 </file>
@@ -678,7 +672,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -816,6 +810,24 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1226,12 +1238,8 @@
       <c r="L2" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="M2" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>57</v>
-      </c>
+      <c r="M2" s="9"/>
+      <c r="N2" s="10"/>
     </row>
     <row r="3" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="28" t="s">
@@ -1248,8 +1256,8 @@
       <c r="J3" s="11"/>
       <c r="K3" s="23"/>
       <c r="L3" s="21"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="22"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="48"/>
     </row>
     <row r="4" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="29" t="s">
@@ -1266,8 +1274,8 @@
       <c r="J4" s="12"/>
       <c r="K4" s="16"/>
       <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="12"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="50"/>
     </row>
     <row r="5" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="29" t="s">
@@ -1284,8 +1292,8 @@
       <c r="J5" s="12"/>
       <c r="K5" s="16"/>
       <c r="L5" s="17"/>
-      <c r="M5" s="17"/>
-      <c r="N5" s="12"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="50"/>
     </row>
     <row r="6" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="29" t="s">
@@ -1302,8 +1310,8 @@
       <c r="J6" s="12"/>
       <c r="K6" s="16"/>
       <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="12"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="50"/>
     </row>
     <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="29" t="s">
@@ -1320,8 +1328,8 @@
       <c r="J7" s="12"/>
       <c r="K7" s="16"/>
       <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="12"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="50"/>
     </row>
     <row r="8" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="29" t="s">
@@ -1338,8 +1346,8 @@
       <c r="J8" s="12"/>
       <c r="K8" s="16"/>
       <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="12"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="50"/>
     </row>
     <row r="9" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="29" t="s">
@@ -1356,8 +1364,8 @@
       <c r="J9" s="12"/>
       <c r="K9" s="16"/>
       <c r="L9" s="17"/>
-      <c r="M9" s="17"/>
-      <c r="N9" s="12"/>
+      <c r="M9" s="49"/>
+      <c r="N9" s="50"/>
     </row>
     <row r="10" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="30" t="s">
@@ -1374,8 +1382,8 @@
       <c r="J10" s="13"/>
       <c r="K10" s="18"/>
       <c r="L10" s="19"/>
-      <c r="M10" s="19"/>
-      <c r="N10" s="13"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="52"/>
     </row>
     <row r="11" spans="1:14" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="27" t="s">
